--- a/docs/IP Address Table.xlsx
+++ b/docs/IP Address Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\8th Sem\Network\Project\Intelligent-Campus-Network-Automation\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Intelligent-Campus-Network-Automation\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C42635D-E044-4F7C-8876-F1B3F996B09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6B11D0-B401-4084-9518-DC0D5F45A417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{54BE8C27-5E95-4FCD-A397-9A57F13C3C61}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{54BE8C27-5E95-4FCD-A397-9A57F13C3C61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="114">
   <si>
     <t>VLAN</t>
   </si>
@@ -117,12 +117,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Fa0/0</t>
-  </si>
-  <si>
-    <t>Fa0/1</t>
-  </si>
-  <si>
     <t>203.0.113.1</t>
   </si>
   <si>
@@ -132,75 +126,6 @@
     <t>/30</t>
   </si>
   <si>
-    <t>Link to R-CORE Fa0/0</t>
-  </si>
-  <si>
-    <r>
-      <t>R-EDGE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Loopback0: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>1.1.1.1/32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - OSPF RID)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>R-CORE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Loopback0: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>2.2.2.2/32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - OSPF RID)</t>
-    </r>
-  </si>
-  <si>
     <t>WAN - link to ISP</t>
   </si>
   <si>
@@ -210,9 +135,6 @@
     <t>192.168.1.1</t>
   </si>
   <si>
-    <t>Link to R-EDGE Fa0/1</t>
-  </si>
-  <si>
     <t>Link to SW-CORE Gi0/0</t>
   </si>
   <si>
@@ -252,18 +174,12 @@
     <t>SW-A-DIS</t>
   </si>
   <si>
-    <t>10.99.99.10</t>
-  </si>
-  <si>
     <t>10.99.99.11</t>
   </si>
   <si>
     <t>10.99.99.12</t>
   </si>
   <si>
-    <t>10.99.99.20</t>
-  </si>
-  <si>
     <t>10.99.99.21</t>
   </si>
   <si>
@@ -312,18 +228,9 @@
     <t>Vlan99 SVI</t>
   </si>
   <si>
-    <t>Loopback0</t>
-  </si>
-  <si>
     <t>192.168.1.2</t>
   </si>
   <si>
-    <t>3.3.3.3</t>
-  </si>
-  <si>
-    <t>/32</t>
-  </si>
-  <si>
     <t>Uplink to R-CORE</t>
   </si>
   <si>
@@ -342,9 +249,6 @@
     <t>Gateway - OOB management</t>
   </si>
   <si>
-    <t>OSPF router ID</t>
-  </si>
-  <si>
     <t>VPC end-hosts (GNS3 - static)</t>
   </si>
   <si>
@@ -375,39 +279,21 @@
     <t>Server-1</t>
   </si>
   <si>
-    <t>Server-2</t>
-  </si>
-  <si>
     <t>VPC-S1</t>
   </si>
   <si>
-    <t>10.10.10.10</t>
-  </si>
-  <si>
     <t>10.10.10.11</t>
   </si>
   <si>
-    <t>10.10.20.10</t>
-  </si>
-  <si>
     <t>10.10.20.11</t>
   </si>
   <si>
-    <t>10.10.30.10</t>
-  </si>
-  <si>
     <t>10.10.30.11</t>
   </si>
   <si>
-    <t>10.10.40.10</t>
-  </si>
-  <si>
     <t>10.10.40.11</t>
   </si>
   <si>
-    <t>10.10.40.20</t>
-  </si>
-  <si>
     <t>Management VMs (VLAN 99)</t>
   </si>
   <si>
@@ -435,9 +321,6 @@
     <t>10.99.99.51</t>
   </si>
   <si>
-    <t>10.99.99.52</t>
-  </si>
-  <si>
     <t>Management switch</t>
   </si>
   <si>
@@ -448,13 +331,49 @@
   </si>
   <si>
     <t>DHCP · DNS · web server</t>
+  </si>
+  <si>
+    <t>Gi0/0</t>
+  </si>
+  <si>
+    <t>Gi0/1</t>
+  </si>
+  <si>
+    <t>Link to R-EDGE Gi0/1</t>
+  </si>
+  <si>
+    <t>Link to R-CORE Gi0/1</t>
+  </si>
+  <si>
+    <t>VPC-S2</t>
+  </si>
+  <si>
+    <t>10.99.99.13</t>
+  </si>
+  <si>
+    <t>10.99.99.24</t>
+  </si>
+  <si>
+    <t>10.10.10.12</t>
+  </si>
+  <si>
+    <t>10.10.20.12</t>
+  </si>
+  <si>
+    <t>10.10.30.12</t>
+  </si>
+  <si>
+    <t>10.10.40.12</t>
+  </si>
+  <si>
+    <t>10.10.40.13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,11 +402,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -519,16 +433,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -681,8 +595,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{488F0A5D-853E-4D5A-A4B1-304B0F1DA37A}" name="Table2" displayName="Table2" ref="B15:E17" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="B15:E17" xr:uid="{488F0A5D-853E-4D5A-A4B1-304B0F1DA37A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{488F0A5D-853E-4D5A-A4B1-304B0F1DA37A}" name="Table2" displayName="Table2" ref="B14:E16" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="B14:E16" xr:uid="{488F0A5D-853E-4D5A-A4B1-304B0F1DA37A}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{70ADE6CE-9A45-494E-860E-B6D998BE6CD6}" name="Interface" dataDxfId="28"/>
     <tableColumn id="2" xr3:uid="{760D590B-145B-4CD6-90FB-ACE7A683889F}" name="IP" dataDxfId="27"/>
@@ -694,34 +608,34 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6048F673-EED8-4CC4-A90A-4330875D755F}" name="Table4" displayName="Table4" ref="B22:E24" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="B22:E24" xr:uid="{6048F673-EED8-4CC4-A90A-4330875D755F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6048F673-EED8-4CC4-A90A-4330875D755F}" name="Table4" displayName="Table4" ref="B20:E22" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+  <autoFilter ref="B20:E22" xr:uid="{6048F673-EED8-4CC4-A90A-4330875D755F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{985ECCDC-5712-4B55-891E-740F2221AA3A}" name="Interface" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{41576E17-B2BA-4F65-AB6E-A6A154223121}" name="IP" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{3D87DFBC-55A7-4D14-B9CC-62E7F26C91DF}" name="Mask" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{64CC4FD6-8836-4683-80D1-3AF4EA2045BE}" name="Description" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{985ECCDC-5712-4B55-891E-740F2221AA3A}" name="Interface" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{41576E17-B2BA-4F65-AB6E-A6A154223121}" name="IP" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{3D87DFBC-55A7-4D14-B9CC-62E7F26C91DF}" name="Mask" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{64CC4FD6-8836-4683-80D1-3AF4EA2045BE}" name="Description" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A6256DAF-00D4-420D-8A9E-6EFC09F00EF2}" name="Table5" displayName="Table5" ref="B29:E36" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="B29:E36" xr:uid="{A6256DAF-00D4-420D-8A9E-6EFC09F00EF2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A6256DAF-00D4-420D-8A9E-6EFC09F00EF2}" name="Table5" displayName="Table5" ref="B27:E34" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="B27:E34" xr:uid="{A6256DAF-00D4-420D-8A9E-6EFC09F00EF2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D8E21B50-B848-4167-A900-9E1E6BAA6CDE}" name="Device" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{3AD86659-8F81-44AC-BB60-11972D3274FA}" name="Vlan99 IP" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{591ECD2E-E45A-4664-A02D-3C970FAEA12F}" name="Data VLAN" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{12ADF382-149F-438B-BB55-7973B2B19A4B}" name="Uplink" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{D8E21B50-B848-4167-A900-9E1E6BAA6CDE}" name="Device" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{3AD86659-8F81-44AC-BB60-11972D3274FA}" name="Vlan99 IP" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{591ECD2E-E45A-4664-A02D-3C970FAEA12F}" name="Data VLAN" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{12ADF382-149F-438B-BB55-7973B2B19A4B}" name="Uplink" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{5113E8E3-2CED-4F0A-8FE5-00607647188E}" name="Table6" displayName="Table6" ref="B41:E48" totalsRowShown="0">
-  <autoFilter ref="B41:E48" xr:uid="{5113E8E3-2CED-4F0A-8FE5-00607647188E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{5113E8E3-2CED-4F0A-8FE5-00607647188E}" name="Table6" displayName="Table6" ref="B39:E45" totalsRowShown="0">
+  <autoFilter ref="B39:E45" xr:uid="{5113E8E3-2CED-4F0A-8FE5-00607647188E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{30E37CDB-D57F-4C83-9821-9C84B10888F1}" name="Interface"/>
     <tableColumn id="2" xr3:uid="{8852305C-9F81-4E1B-A0EF-D70050FAE230}" name="IP"/>
@@ -733,27 +647,27 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{93C47417-70CF-4C7B-871E-F825F6F0E3F0}" name="Table7" displayName="Table7" ref="B53:F62" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="B53:F62" xr:uid="{93C47417-70CF-4C7B-871E-F825F6F0E3F0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{93C47417-70CF-4C7B-871E-F825F6F0E3F0}" name="Table7" displayName="Table7" ref="B50:F59" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="B50:F59" xr:uid="{93C47417-70CF-4C7B-871E-F825F6F0E3F0}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{CF710A36-83DB-4A97-AB40-6A1F15B97770}" name="Host" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{27FFAF5F-9CC0-4DA0-8F3F-C9335BCFB45D}" name="VLAN" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{ABA6B139-2EF9-4837-8BEA-446D2381DD17}" name="IP" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{CEBDBD3E-66F5-4E42-8C9A-8A4790B1903D}" name="Mask" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{1FACF4A3-F646-4689-AA07-DCF162CB923C}" name="Gateway" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{CF710A36-83DB-4A97-AB40-6A1F15B97770}" name="Host" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{27FFAF5F-9CC0-4DA0-8F3F-C9335BCFB45D}" name="VLAN" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{ABA6B139-2EF9-4837-8BEA-446D2381DD17}" name="IP" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{CEBDBD3E-66F5-4E42-8C9A-8A4790B1903D}" name="Mask" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{1FACF4A3-F646-4689-AA07-DCF162CB923C}" name="Gateway" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0365DC01-9C02-4068-921F-4C9621A93729}" name="Table8" displayName="Table8" ref="B67:E71" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="B67:E71" xr:uid="{0365DC01-9C02-4068-921F-4C9621A93729}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0365DC01-9C02-4068-921F-4C9621A93729}" name="Table8" displayName="Table8" ref="B63:E67" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="B63:E67" xr:uid="{0365DC01-9C02-4068-921F-4C9621A93729}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D3EF669E-597B-4F98-8399-A2BCAC11C1BF}" name="VM" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{CDE2A659-BE47-4803-9438-C187F2CB0BD5}" name="IP" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{2704067F-F6FA-4335-8B1D-F33FD4DE5591}" name="Gateway" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{66BFA613-82A9-450E-B2CB-DB7EE038F27B}" name="Role" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{D3EF669E-597B-4F98-8399-A2BCAC11C1BF}" name="VM" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{CDE2A659-BE47-4803-9438-C187F2CB0BD5}" name="IP" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{2704067F-F6FA-4335-8B1D-F33FD4DE5591}" name="Gateway" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{66BFA613-82A9-450E-B2CB-DB7EE038F27B}" name="Role" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1056,8 +970,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029A1262-5287-4F3A-8292-B93C7B108AC8}">
-  <dimension ref="B1:G71"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B1:G67"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
@@ -1067,19 +981,19 @@
     <col min="7" max="7" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="2:7">
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="2:7">
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>10</v>
       </c>
@@ -1119,7 +1033,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>20</v>
       </c>
@@ -1139,7 +1053,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>30</v>
       </c>
@@ -1159,7 +1073,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>40</v>
       </c>
@@ -1179,7 +1093,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>99</v>
       </c>
@@ -1199,611 +1113,581 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="18">
-      <c r="B11" s="4" t="s">
+    <row r="11" spans="2:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="B11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="5" t="s">
+      <c r="C11" s="5"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="2" t="s">
+    </row>
+    <row r="25" spans="2:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="1">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="1">
+        <v>20</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="1">
+        <v>30</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="1">
+        <v>10</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="1">
+        <v>20</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="1">
+        <v>30</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="1">
+        <v>40</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C39" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D39" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="1" t="s">
+      <c r="E39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="B48" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52" s="1">
+        <v>10</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" s="1">
+        <v>20</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" s="1">
+        <v>20</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="1">
         <v>30</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="D55" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="1">
+        <v>30</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C57" s="1">
+        <v>40</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C58" s="1">
+        <v>40</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" s="1">
+        <v>40</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="B61" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="18">
-      <c r="B27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="1">
-        <v>10</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="1">
+      <c r="D63" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="1">
-        <v>30</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" s="1">
-        <v>10</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="1">
-        <v>20</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="1">
-        <v>30</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="1">
-        <v>40</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" s="5"/>
-    </row>
-    <row r="41" spans="2:5">
-      <c r="B41" t="s">
-        <v>26</v>
-      </c>
-      <c r="C41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5">
-      <c r="B42" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5">
-      <c r="B43" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="B44" t="s">
-        <v>71</v>
-      </c>
-      <c r="C44" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="B45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="B46" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" t="s">
-        <v>20</v>
-      </c>
-      <c r="D46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="B47" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5">
-      <c r="B48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" t="s">
-        <v>77</v>
-      </c>
-      <c r="D48" t="s">
-        <v>78</v>
-      </c>
-      <c r="E48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" ht="18">
-      <c r="B51" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C54" s="1">
-        <v>10</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6">
-      <c r="B55" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" s="1">
-        <v>10</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6">
-      <c r="B56" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" s="1">
-        <v>20</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" s="1">
-        <v>20</v>
-      </c>
-      <c r="D57" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" s="1">
-        <v>30</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6">
-      <c r="B59" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" s="1">
-        <v>30</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6">
-      <c r="B60" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C60" s="1">
-        <v>40</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C61" s="1">
-        <v>40</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6">
-      <c r="B62" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C62" s="1">
-        <v>40</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" ht="18">
-      <c r="B65" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-    </row>
-    <row r="67" spans="2:5">
-      <c r="B67" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5">
-      <c r="B68" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5">
-      <c r="B69" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5">
-      <c r="B70" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5">
-      <c r="B71" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>120</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B51:D51"/>
+  <mergeCells count="6">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B48:D48"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B25:D25"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/IP Address Table.xlsx
+++ b/docs/IP Address Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Intelligent-Campus-Network-Automation\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Gihan\Project\Intelligent-Campus-Network-Automation\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6B11D0-B401-4084-9518-DC0D5F45A417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38374DA-F218-4129-9869-E273EA96D21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{54BE8C27-5E95-4FCD-A397-9A57F13C3C61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{54BE8C27-5E95-4FCD-A397-9A57F13C3C61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -276,9 +276,6 @@
     <t>VPC-M2</t>
   </si>
   <si>
-    <t>Server-1</t>
-  </si>
-  <si>
     <t>VPC-S1</t>
   </si>
   <si>
@@ -367,6 +364,9 @@
   </si>
   <si>
     <t>10.10.40.13</t>
+  </si>
+  <si>
+    <t>VM-DHCP</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>30</v>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>31</v>
@@ -1158,7 +1158,7 @@
         <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
@@ -1177,7 +1177,7 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>34</v>
@@ -1186,12 +1186,12 @@
         <v>32</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>35</v>
@@ -1257,7 +1257,7 @@
         <v>44</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D30" s="1">
         <v>30</v>
@@ -1313,7 +1313,7 @@
         <v>48</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D34" s="1">
         <v>40</v>
@@ -1458,7 +1458,7 @@
         <v>10</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>18</v>
@@ -1475,7 +1475,7 @@
         <v>10</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>18</v>
@@ -1492,7 +1492,7 @@
         <v>20</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>18</v>
@@ -1509,7 +1509,7 @@
         <v>20</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>18</v>
@@ -1526,7 +1526,7 @@
         <v>30</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>18</v>
@@ -1543,7 +1543,7 @@
         <v>30</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>18</v>
@@ -1554,13 +1554,13 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C57" s="1">
         <v>40</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>18</v>
@@ -1571,13 +1571,13 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C58" s="1">
         <v>40</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>18</v>
@@ -1588,13 +1588,13 @@
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C59" s="1">
         <v>40</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>18</v>
@@ -1605,14 +1605,14 @@
     </row>
     <row r="61" spans="2:6" ht="18" x14ac:dyDescent="0.3">
       <c r="B61" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>27</v>
@@ -1626,58 +1626,58 @@
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
